--- a/data/excel/example-input.xlsx
+++ b/data/excel/example-input.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7305AFEE-9277-46BA-BAAD-B322BCC9AA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B72E79-CBB4-40CB-9792-7EAE1236A0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>Policy Number</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Snehal Savant</t>
+  </si>
+  <si>
+    <t>Vitthal Savant</t>
   </si>
 </sst>
 </file>
@@ -467,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -616,13 +619,49 @@
         <v>46127</v>
       </c>
     </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>429762163</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7559214300</v>
+      </c>
+      <c r="D5">
+        <v>3856</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46092</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="1">
+        <v>46127</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{9765B895-9E76-4EAC-BECB-D8751064612F}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{E3FF5829-81A7-41EE-B610-BE06FA1FF941}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{FFCFDE73-1563-4BE6-B30C-7A7B1C515F1D}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{9FA018FA-CFA4-41EA-A492-A840E8B5791B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId4"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId5"/>
 </worksheet>
 </file>